--- a/Documents/เฉพาะคราว/SA_Spec_Narcotic4_Temporary_IMP_rev.1.2.xlsx
+++ b/Documents/เฉพาะคราว/SA_Spec_Narcotic4_Temporary_IMP_rev.1.2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\NCSystem\brain_NCSYSTEM\Documents\เฉพาะคราว\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4382429D-2BE4-46E4-A2E9-174EE4823BAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65FB87D0-7178-4DE0-AC48-566CDF4BE674}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="766" uniqueCount="444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="919" uniqueCount="436">
   <si>
     <t>ยส.4 เฉพาะคราว นำเข้า (IMP-N4-1) — SA Spec DRAFT</t>
   </si>
@@ -980,95 +980,21 @@
     <t>Step 4: เอกสารหลักฐาน (ส่วนที่ ๓) — 2 Conditional Cases</t>
   </si>
   <si>
-    <t>3.0 Case Selection — เลือกกรณีการขอนำเข้า</t>
-  </si>
-  <si>
-    <t>กรณีการขอ</t>
-  </si>
-  <si>
-    <t>Case Type</t>
-  </si>
-  <si>
     <t>AttachmentCase</t>
   </si>
   <si>
-    <t>??? (ต้องเพิ่ม column หรือ derive)</t>
-  </si>
-  <si>
-    <t>char(1) or nvarchar</t>
-  </si>
-  <si>
-    <t>hard-coded (I/R)</t>
-  </si>
-  <si>
-    <t>2 options:
-  I = อุตสาหกรรม (Industrial)
-  R = สารมาตรฐานปริมาณเล็กน้อย (Reference Standard)</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>ต้องถามว่าจะเก็บเป็น column หรือ derive จาก attachment type</t>
-  </si>
-  <si>
-    <t>3.1 กรณีที่ 1: เพื่อใช้ประโยชน์ทางอุตสาหกรรม (Industrial) — show if Case=I</t>
-  </si>
-  <si>
-    <t>ใบสั่งซื้อ (PO)</t>
-  </si>
-  <si>
-    <t>Purchase Order (PO)</t>
-  </si>
-  <si>
-    <t>AttachmentPO</t>
-  </si>
-  <si>
     <t>file</t>
   </si>
   <si>
-    <t>required if Case=I</t>
-  </si>
-  <si>
     <t>RequisitionDocumentAttachment</t>
   </si>
   <si>
-    <t>AttachmentTypeId='PO' + FilePath</t>
-  </si>
-  <si>
     <t>MasterAttachmentType</t>
   </si>
   <si>
     <t>accept .pdf, .jpg, .png; max 10MB</t>
   </si>
   <si>
-    <t>3.1</t>
-  </si>
-  <si>
-    <t>MasterAttachmentType ต้องมี seed 'PO'</t>
-  </si>
-  <si>
-    <t>แผนการใช้ประโยชน์และปริมาณการใช้</t>
-  </si>
-  <si>
-    <t>Usage Plan &amp; Quantity</t>
-  </si>
-  <si>
-    <t>AttachmentUsagePlan</t>
-  </si>
-  <si>
-    <t>AttachmentTypeId='UsagePlan' + FilePath</t>
-  </si>
-  <si>
-    <t>accept .pdf, .doc, .docx; max 10MB</t>
-  </si>
-  <si>
-    <t>หรือรวมกับ PO เป็นไฟล์เดียว?</t>
-  </si>
-  <si>
-    <t>3.2 กรณีที่ 2: นำเข้าสารมาตรฐานในปริมาณเล็กน้อย (Reference Std) — show if Case=R</t>
-  </si>
-  <si>
     <t>ใบวิเคราะห์คุณภาพ COA</t>
   </si>
   <si>
@@ -1078,37 +1004,7 @@
     <t>AttachmentCOA</t>
   </si>
   <si>
-    <t>required if Case=R</t>
-  </si>
-  <si>
-    <t>AttachmentTypeId='COA' + FilePath</t>
-  </si>
-  <si>
     <t>3.2</t>
-  </si>
-  <si>
-    <t>PDF บอก 'COA หรือข้อมูลผลิตภัณฑ์' — อาจยอมรับ product info แทนได้</t>
-  </si>
-  <si>
-    <t>ข้อมูลผลิตภัณฑ์ (alternative)</t>
-  </si>
-  <si>
-    <t>Product Information</t>
-  </si>
-  <si>
-    <t>AttachmentProductInfo</t>
-  </si>
-  <si>
-    <t>alternative to COA</t>
-  </si>
-  <si>
-    <t>AttachmentTypeId='ProductInfo' + FilePath</t>
-  </si>
-  <si>
-    <t>accept .pdf, .doc; max 10MB</t>
-  </si>
-  <si>
-    <t>optional alternative</t>
   </si>
   <si>
     <t>DB Mapping Summary — ตาราง DAL ที่ใช้</t>
@@ -1389,12 +1285,90 @@
   <si>
     <t>ต้องดูวัตถุประสงค์ของใบอนุญาตประกอบ</t>
   </si>
+  <si>
+    <t>หนังสือแจ้งความประสงค์ในการส่งออกจากหัวหน้าส่วนราชการซึ่งเป็นนิติบุคคล</t>
+  </si>
+  <si>
+    <t>ข้อมูลผลิตภัณฑ์</t>
+  </si>
+  <si>
+    <t>โครงการวิจัย</t>
+  </si>
+  <si>
+    <t>ใบสั่งซื้อ (Purchase order: PO)</t>
+  </si>
+  <si>
+    <t>ใบตอบรับการสั่งซื้อ (Order Acknowledgement/Sale Contract) ที่มีการระบุหมายเลข ใบสั่งซื้อ (PO no.)</t>
+  </si>
+  <si>
+    <t>หนังสือรับรองแผนการใช้ประโยชน์และปริมาณการใช้ Acetic anhydride</t>
+  </si>
+  <si>
+    <t>required if IsRequire = 1 from MasterExportImportAttachmentTypeConfig where RequisitionTypeId = 31 and ObjectiveId = 14</t>
+  </si>
+  <si>
+    <t>AttachmentTypeId='318'+ FilePath</t>
+  </si>
+  <si>
+    <t>AttachmentTypeId='319'+ FilePath</t>
+  </si>
+  <si>
+    <t>AttachmentTypeId='320'+ FilePath</t>
+  </si>
+  <si>
+    <t>AttachmentTypeId='321'+ FilePath</t>
+  </si>
+  <si>
+    <t>3.1 ผู้ขอ - หน่วยงานของรัฐที่เป็นนิติบุคคล — ApplicantType = 13</t>
+  </si>
+  <si>
+    <t>3.1.1 กรณีที่ 1: เพื่อประโยชน์ของทางราชการในการป้องกันและปราบปรามการกระทำความผิดเกี่ยวกับยาเสพติดหรือความร่วมมือระหว่างประเทศในกรณีจำเป็นเร่งด่วน ตามมาตรา 34 วรรค 1 — Requisition.RequisitionTypeId = 31 and License.ObjectiveId = 14</t>
+  </si>
+  <si>
+    <t>3.1.2 กรณีที่ 2: เพื่อการศึกษาวิจัย หรือเพื่อประโยชน์ในทางการแพทย์หรือวิทยาศาสตร์ ตามมาตรา 34 วรรค 2 — Requisition.RequisitionTypeId = 31 and License.ObjectiveId = 15 or 16 or 17</t>
+  </si>
+  <si>
+    <t>3.2 ผู้ขอ - อื่น ๆ — ApplicantType &lt;&gt; 13</t>
+  </si>
+  <si>
+    <t>3.2.1 กรณีที่ 1: เพื่อการศึกษาวิจัย หรือเพื่อประโยชน์ในทางการแพทย์หรือวิทยาศาสตร์ ตามมาตรา 34 วรรค 2 — Requisition.RequisitionTypeId = 31 and License.ObjectiveId = 15 or 16 or 17</t>
+  </si>
+  <si>
+    <t>required if IsRequire = 1 from MasterExportImportAttachmentTypeConfig where RequisitionTypeId = 31 and ObjectiveId = 15 or 16 or 17</t>
+  </si>
+  <si>
+    <t>3.1.3 กรณีที่ 3: เพื่อใช้เป็นสารมาตรฐานในการตรวจวิเคราะห์ในปริมาณเล็กน้อย ตามมาตรา 35 (3) — Requisition.RequisitionTypeId = 31 and License.ObjectiveId = 19</t>
+  </si>
+  <si>
+    <t>required if IsRequire = 1 from MasterExportImportAttachmentTypeConfig where RequisitionTypeId = 31 and ObjectiveId = 19</t>
+  </si>
+  <si>
+    <t>3.2.2 กรณีที่ 2: เพื่อประโยชน์ทางอุตสาหกรรม (กรณีสถานที่นำเข้าและสถานที่เก็บเป็นสถานที่เดียวกัน) — Requisition.RequisitionTypeId = 31 and License.ObjectiveId = 18</t>
+  </si>
+  <si>
+    <t>3.2.3 กรณีที่ 3: เพื่อประโยชน์ทางอุตสาหกรรม (กรณีสถานที่นำเข้าและสถานที่เก็บคนละสถานที่) — Requisition.RequisitionTypeId = 31 and License.ObjectiveId = 18</t>
+  </si>
+  <si>
+    <t>required if IsRequire = 1 from MasterExportImportAttachmentTypeConfig where RequisitionTypeId = 31 and ObjectiveId = 18</t>
+  </si>
+  <si>
+    <t>AttachmentTypeId='322'+ FilePath</t>
+  </si>
+  <si>
+    <t>AttachmentTypeId='323'+ FilePath</t>
+  </si>
+  <si>
+    <t>AttachmentTypeId='324'+ FilePath</t>
+  </si>
+  <si>
+    <t>3.2.4 กรณีที่ 4: เพื่อใช้เป็นสารมาตรฐานในการตรวจวิเคราะห์ในปริมาณเล็กน้อย ตามมาตรา 35 (3) — Requisition.RequisitionTypeId = 31 and License.ObjectiveId = 19</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1506,8 +1480,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1550,6 +1531,12 @@
         <bgColor rgb="FF8497B0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8497B0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -1578,7 +1565,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1622,6 +1609,13 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1633,27 +1627,32 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1661,6 +1660,12 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF8497B0"/>
+      <color rgb="FF4472C4"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -2059,7 +2064,7 @@
         <v>22</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>427</v>
+        <v>393</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -2145,10 +2150,10 @@
       </c>
     </row>
     <row r="28" spans="1:2" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="25" t="s">
+      <c r="A28" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="B28" s="24"/>
+      <c r="B28" s="27"/>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
@@ -2156,46 +2161,46 @@
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="23" t="s">
+      <c r="A31" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="B31" s="24"/>
+      <c r="B31" s="27"/>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="23" t="s">
+      <c r="A32" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="B32" s="24"/>
+      <c r="B32" s="27"/>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="23" t="s">
+      <c r="A33" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="B33" s="24"/>
+      <c r="B33" s="27"/>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="23" t="s">
+      <c r="A34" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="B34" s="24"/>
+      <c r="B34" s="27"/>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="23" t="s">
+      <c r="A35" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="B35" s="24"/>
+      <c r="B35" s="27"/>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="23" t="s">
+      <c r="A36" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="B36" s="24"/>
+      <c r="B36" s="27"/>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="23" t="s">
+      <c r="A37" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="B37" s="24"/>
+      <c r="B37" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -2397,10 +2402,10 @@
       </c>
     </row>
     <row r="28" spans="1:2" ht="110.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="25" t="s">
+      <c r="A28" s="28" t="s">
         <v>95</v>
       </c>
-      <c r="B28" s="24"/>
+      <c r="B28" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2433,24 +2438,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
-      <c r="M1" s="24"/>
-      <c r="N1" s="24"/>
-      <c r="O1" s="24"/>
-      <c r="P1" s="24"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
+      <c r="O1" s="27"/>
+      <c r="P1" s="27"/>
     </row>
     <row r="3" spans="1:16" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
@@ -2503,24 +2508,24 @@
       </c>
     </row>
     <row r="4" spans="1:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="29" t="s">
         <v>97</v>
       </c>
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="24"/>
-      <c r="G4" s="24"/>
-      <c r="H4" s="24"/>
-      <c r="I4" s="24"/>
-      <c r="J4" s="24"/>
-      <c r="K4" s="24"/>
-      <c r="L4" s="24"/>
-      <c r="M4" s="24"/>
-      <c r="N4" s="24"/>
-      <c r="O4" s="24"/>
-      <c r="P4" s="24"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
+      <c r="H4" s="27"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="27"/>
+      <c r="K4" s="27"/>
+      <c r="L4" s="27"/>
+      <c r="M4" s="27"/>
+      <c r="N4" s="27"/>
+      <c r="O4" s="27"/>
+      <c r="P4" s="27"/>
     </row>
     <row r="5" spans="1:16" ht="84" x14ac:dyDescent="0.25">
       <c r="A5" s="10">
@@ -2567,7 +2572,7 @@
       </c>
       <c r="O5" s="10"/>
       <c r="P5" s="10" t="s">
-        <v>438</v>
+        <v>404</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="24" x14ac:dyDescent="0.25">
@@ -2590,13 +2595,13 @@
         <v>102</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>431</v>
+        <v>397</v>
       </c>
       <c r="H6" s="10" t="s">
         <v>103</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>429</v>
+        <v>395</v>
       </c>
       <c r="J6" s="10" t="s">
         <v>111</v>
@@ -2638,13 +2643,13 @@
         <v>102</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>432</v>
+        <v>398</v>
       </c>
       <c r="H7" s="10" t="s">
         <v>103</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>428</v>
+        <v>394</v>
       </c>
       <c r="J7" s="10" t="s">
         <v>104</v>
@@ -2663,28 +2668,28 @@
       </c>
       <c r="O7" s="10"/>
       <c r="P7" s="10" t="s">
-        <v>430</v>
+        <v>396</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="26" t="s">
+      <c r="A9" s="29" t="s">
         <v>127</v>
       </c>
-      <c r="B9" s="24"/>
-      <c r="C9" s="24"/>
-      <c r="D9" s="24"/>
-      <c r="E9" s="24"/>
-      <c r="F9" s="24"/>
-      <c r="G9" s="24"/>
-      <c r="H9" s="24"/>
-      <c r="I9" s="24"/>
-      <c r="J9" s="24"/>
-      <c r="K9" s="24"/>
-      <c r="L9" s="24"/>
-      <c r="M9" s="24"/>
-      <c r="N9" s="24"/>
-      <c r="O9" s="24"/>
-      <c r="P9" s="24"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="27"/>
+      <c r="G9" s="27"/>
+      <c r="H9" s="27"/>
+      <c r="I9" s="27"/>
+      <c r="J9" s="27"/>
+      <c r="K9" s="27"/>
+      <c r="L9" s="27"/>
+      <c r="M9" s="27"/>
+      <c r="N9" s="27"/>
+      <c r="O9" s="27"/>
+      <c r="P9" s="27"/>
     </row>
     <row r="10" spans="1:16" ht="24" x14ac:dyDescent="0.25">
       <c r="A10" s="10">
@@ -2712,10 +2717,10 @@
         <v>120</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>433</v>
+        <v>399</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>434</v>
+        <v>400</v>
       </c>
       <c r="K10" s="10" t="s">
         <v>112</v>
@@ -2731,7 +2736,7 @@
       </c>
       <c r="O10" s="10"/>
       <c r="P10" s="10" t="s">
-        <v>437</v>
+        <v>403</v>
       </c>
     </row>
   </sheetData>
@@ -2767,24 +2772,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="30" t="s">
         <v>134</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
-      <c r="M1" s="24"/>
-      <c r="N1" s="24"/>
-      <c r="O1" s="24"/>
-      <c r="P1" s="24"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
+      <c r="O1" s="27"/>
+      <c r="P1" s="27"/>
     </row>
     <row r="3" spans="1:16" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
@@ -2837,24 +2842,24 @@
       </c>
     </row>
     <row r="4" spans="1:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="29" t="s">
         <v>135</v>
       </c>
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="24"/>
-      <c r="G4" s="24"/>
-      <c r="H4" s="24"/>
-      <c r="I4" s="24"/>
-      <c r="J4" s="24"/>
-      <c r="K4" s="24"/>
-      <c r="L4" s="24"/>
-      <c r="M4" s="24"/>
-      <c r="N4" s="24"/>
-      <c r="O4" s="24"/>
-      <c r="P4" s="24"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
+      <c r="H4" s="27"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="27"/>
+      <c r="K4" s="27"/>
+      <c r="L4" s="27"/>
+      <c r="M4" s="27"/>
+      <c r="N4" s="27"/>
+      <c r="O4" s="27"/>
+      <c r="P4" s="27"/>
     </row>
     <row r="5" spans="1:16" ht="24" x14ac:dyDescent="0.25">
       <c r="A5" s="10">
@@ -2999,24 +3004,24 @@
       </c>
     </row>
     <row r="9" spans="1:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="26" t="s">
+      <c r="A9" s="29" t="s">
         <v>159</v>
       </c>
-      <c r="B9" s="24"/>
-      <c r="C9" s="24"/>
-      <c r="D9" s="24"/>
-      <c r="E9" s="24"/>
-      <c r="F9" s="24"/>
-      <c r="G9" s="24"/>
-      <c r="H9" s="24"/>
-      <c r="I9" s="24"/>
-      <c r="J9" s="24"/>
-      <c r="K9" s="24"/>
-      <c r="L9" s="24"/>
-      <c r="M9" s="24"/>
-      <c r="N9" s="24"/>
-      <c r="O9" s="24"/>
-      <c r="P9" s="24"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="27"/>
+      <c r="G9" s="27"/>
+      <c r="H9" s="27"/>
+      <c r="I9" s="27"/>
+      <c r="J9" s="27"/>
+      <c r="K9" s="27"/>
+      <c r="L9" s="27"/>
+      <c r="M9" s="27"/>
+      <c r="N9" s="27"/>
+      <c r="O9" s="27"/>
+      <c r="P9" s="27"/>
     </row>
     <row r="10" spans="1:16" ht="24" x14ac:dyDescent="0.25">
       <c r="A10" s="10">
@@ -3157,24 +3162,24 @@
       <c r="P12" s="10"/>
     </row>
     <row r="14" spans="1:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="26" t="s">
+      <c r="A14" s="29" t="s">
         <v>176</v>
       </c>
-      <c r="B14" s="24"/>
-      <c r="C14" s="24"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="24"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="24"/>
-      <c r="I14" s="24"/>
-      <c r="J14" s="24"/>
-      <c r="K14" s="24"/>
-      <c r="L14" s="24"/>
-      <c r="M14" s="24"/>
-      <c r="N14" s="24"/>
-      <c r="O14" s="24"/>
-      <c r="P14" s="24"/>
+      <c r="B14" s="27"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="27"/>
+      <c r="G14" s="27"/>
+      <c r="H14" s="27"/>
+      <c r="I14" s="27"/>
+      <c r="J14" s="27"/>
+      <c r="K14" s="27"/>
+      <c r="L14" s="27"/>
+      <c r="M14" s="27"/>
+      <c r="N14" s="27"/>
+      <c r="O14" s="27"/>
+      <c r="P14" s="27"/>
     </row>
     <row r="15" spans="1:16" ht="24" x14ac:dyDescent="0.25">
       <c r="A15" s="10">
@@ -3315,24 +3320,24 @@
       <c r="P17" s="10"/>
     </row>
     <row r="19" spans="1:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="26" t="s">
+      <c r="A19" s="29" t="s">
         <v>190</v>
       </c>
-      <c r="B19" s="24"/>
-      <c r="C19" s="24"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="24"/>
-      <c r="G19" s="24"/>
-      <c r="H19" s="24"/>
-      <c r="I19" s="24"/>
-      <c r="J19" s="24"/>
-      <c r="K19" s="24"/>
-      <c r="L19" s="24"/>
-      <c r="M19" s="24"/>
-      <c r="N19" s="24"/>
-      <c r="O19" s="24"/>
-      <c r="P19" s="24"/>
+      <c r="B19" s="27"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="27"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="27"/>
+      <c r="H19" s="27"/>
+      <c r="I19" s="27"/>
+      <c r="J19" s="27"/>
+      <c r="K19" s="27"/>
+      <c r="L19" s="27"/>
+      <c r="M19" s="27"/>
+      <c r="N19" s="27"/>
+      <c r="O19" s="27"/>
+      <c r="P19" s="27"/>
     </row>
     <row r="20" spans="1:16" ht="24" x14ac:dyDescent="0.25">
       <c r="A20" s="10">
@@ -3454,7 +3459,7 @@
         <v>120</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>435</v>
+        <v>401</v>
       </c>
       <c r="J22" s="10" t="s">
         <v>155</v>
@@ -3473,28 +3478,28 @@
       </c>
       <c r="O22" s="10"/>
       <c r="P22" s="10" t="s">
-        <v>436</v>
+        <v>402</v>
       </c>
     </row>
     <row r="24" spans="1:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="26" t="s">
+      <c r="A24" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="B24" s="24"/>
-      <c r="C24" s="24"/>
-      <c r="D24" s="24"/>
-      <c r="E24" s="24"/>
-      <c r="F24" s="24"/>
-      <c r="G24" s="24"/>
-      <c r="H24" s="24"/>
-      <c r="I24" s="24"/>
-      <c r="J24" s="24"/>
-      <c r="K24" s="24"/>
-      <c r="L24" s="24"/>
-      <c r="M24" s="24"/>
-      <c r="N24" s="24"/>
-      <c r="O24" s="24"/>
-      <c r="P24" s="24"/>
+      <c r="B24" s="27"/>
+      <c r="C24" s="27"/>
+      <c r="D24" s="27"/>
+      <c r="E24" s="27"/>
+      <c r="F24" s="27"/>
+      <c r="G24" s="27"/>
+      <c r="H24" s="27"/>
+      <c r="I24" s="27"/>
+      <c r="J24" s="27"/>
+      <c r="K24" s="27"/>
+      <c r="L24" s="27"/>
+      <c r="M24" s="27"/>
+      <c r="N24" s="27"/>
+      <c r="O24" s="27"/>
+      <c r="P24" s="27"/>
     </row>
     <row r="25" spans="1:16" ht="24" x14ac:dyDescent="0.25">
       <c r="A25" s="10">
@@ -3569,7 +3574,7 @@
     <col min="5" max="5" width="15" customWidth="1"/>
     <col min="6" max="6" width="10" customWidth="1"/>
     <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="26" customWidth="1"/>
+    <col min="8" max="8" width="26.42578125" customWidth="1"/>
     <col min="9" max="9" width="30" customWidth="1"/>
     <col min="10" max="10" width="16" customWidth="1"/>
     <col min="11" max="11" width="20" customWidth="1"/>
@@ -3580,44 +3585,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="30" t="s">
         <v>219</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
-      <c r="M1" s="24"/>
-      <c r="N1" s="24"/>
-      <c r="O1" s="24"/>
-      <c r="P1" s="24"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
+      <c r="O1" s="27"/>
+      <c r="P1" s="27"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="31" t="s">
         <v>220</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="24"/>
-      <c r="L2" s="24"/>
-      <c r="M2" s="24"/>
-      <c r="N2" s="24"/>
-      <c r="O2" s="24"/>
-      <c r="P2" s="24"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
+      <c r="K2" s="27"/>
+      <c r="L2" s="27"/>
+      <c r="M2" s="27"/>
+      <c r="N2" s="27"/>
+      <c r="O2" s="27"/>
+      <c r="P2" s="27"/>
     </row>
     <row r="4" spans="1:16" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
@@ -3670,24 +3675,24 @@
       </c>
     </row>
     <row r="5" spans="1:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="29" t="s">
         <v>221</v>
       </c>
-      <c r="B5" s="24"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="24"/>
-      <c r="E5" s="24"/>
-      <c r="F5" s="24"/>
-      <c r="G5" s="24"/>
-      <c r="H5" s="24"/>
-      <c r="I5" s="24"/>
-      <c r="J5" s="24"/>
-      <c r="K5" s="24"/>
-      <c r="L5" s="24"/>
-      <c r="M5" s="24"/>
-      <c r="N5" s="24"/>
-      <c r="O5" s="24"/>
-      <c r="P5" s="24"/>
+      <c r="B5" s="27"/>
+      <c r="C5" s="27"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="27"/>
+      <c r="F5" s="27"/>
+      <c r="G5" s="27"/>
+      <c r="H5" s="27"/>
+      <c r="I5" s="27"/>
+      <c r="J5" s="27"/>
+      <c r="K5" s="27"/>
+      <c r="L5" s="27"/>
+      <c r="M5" s="27"/>
+      <c r="N5" s="27"/>
+      <c r="O5" s="27"/>
+      <c r="P5" s="27"/>
     </row>
     <row r="6" spans="1:16" ht="24" x14ac:dyDescent="0.25">
       <c r="A6" s="10">
@@ -4216,68 +4221,68 @@
       </c>
     </row>
     <row r="19" spans="1:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="32" t="s">
+      <c r="A19" s="35" t="s">
         <v>290</v>
       </c>
-      <c r="B19" s="24"/>
-      <c r="C19" s="24"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="24"/>
-      <c r="G19" s="24"/>
-      <c r="H19" s="24"/>
-      <c r="I19" s="24"/>
-      <c r="J19" s="24"/>
-      <c r="K19" s="24"/>
-      <c r="L19" s="24"/>
-      <c r="M19" s="24"/>
-      <c r="N19" s="24"/>
-      <c r="O19" s="24"/>
-      <c r="P19" s="24"/>
+      <c r="B19" s="27"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="27"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="27"/>
+      <c r="H19" s="27"/>
+      <c r="I19" s="27"/>
+      <c r="J19" s="27"/>
+      <c r="K19" s="27"/>
+      <c r="L19" s="27"/>
+      <c r="M19" s="27"/>
+      <c r="N19" s="27"/>
+      <c r="O19" s="27"/>
+      <c r="P19" s="27"/>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20" s="30" t="s">
+      <c r="A20" s="38" t="s">
         <v>291</v>
       </c>
-      <c r="B20" s="24"/>
-      <c r="C20" s="24"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="24"/>
-      <c r="F20" s="24"/>
-      <c r="G20" s="24"/>
-      <c r="H20" s="24"/>
-      <c r="I20" s="24"/>
-      <c r="J20" s="24"/>
-      <c r="K20" s="24"/>
-      <c r="L20" s="24"/>
-      <c r="M20" s="24"/>
-      <c r="N20" s="24"/>
-      <c r="O20" s="24"/>
-      <c r="P20" s="24"/>
+      <c r="B20" s="27"/>
+      <c r="C20" s="27"/>
+      <c r="D20" s="27"/>
+      <c r="E20" s="27"/>
+      <c r="F20" s="27"/>
+      <c r="G20" s="27"/>
+      <c r="H20" s="27"/>
+      <c r="I20" s="27"/>
+      <c r="J20" s="27"/>
+      <c r="K20" s="27"/>
+      <c r="L20" s="27"/>
+      <c r="M20" s="27"/>
+      <c r="N20" s="27"/>
+      <c r="O20" s="27"/>
+      <c r="P20" s="27"/>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" s="29" t="s">
+      <c r="A21" s="32" t="s">
         <v>292</v>
       </c>
-      <c r="B21" s="24"/>
-      <c r="C21" s="24"/>
-      <c r="D21" s="24"/>
+      <c r="B21" s="27"/>
+      <c r="C21" s="27"/>
+      <c r="D21" s="27"/>
       <c r="E21" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="F21" s="28" t="s">
+      <c r="F21" s="36" t="s">
         <v>294</v>
       </c>
-      <c r="G21" s="24"/>
-      <c r="H21" s="24"/>
-      <c r="I21" s="24"/>
-      <c r="J21" s="24"/>
-      <c r="K21" s="24"/>
-      <c r="L21" s="24"/>
-      <c r="M21" s="24"/>
-      <c r="N21" s="24"/>
-      <c r="O21" s="24"/>
-      <c r="P21" s="24"/>
+      <c r="G21" s="27"/>
+      <c r="H21" s="27"/>
+      <c r="I21" s="27"/>
+      <c r="J21" s="27"/>
+      <c r="K21" s="27"/>
+      <c r="L21" s="27"/>
+      <c r="M21" s="27"/>
+      <c r="N21" s="27"/>
+      <c r="O21" s="27"/>
+      <c r="P21" s="27"/>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E22" s="6" t="s">
@@ -4286,58 +4291,58 @@
       <c r="F22" s="33" t="s">
         <v>296</v>
       </c>
-      <c r="G22" s="24"/>
-      <c r="H22" s="24"/>
-      <c r="I22" s="24"/>
-      <c r="J22" s="24"/>
-      <c r="K22" s="24"/>
-      <c r="L22" s="24"/>
-      <c r="M22" s="24"/>
-      <c r="N22" s="24"/>
-      <c r="O22" s="24"/>
-      <c r="P22" s="24"/>
+      <c r="G22" s="27"/>
+      <c r="H22" s="27"/>
+      <c r="I22" s="27"/>
+      <c r="J22" s="27"/>
+      <c r="K22" s="27"/>
+      <c r="L22" s="27"/>
+      <c r="M22" s="27"/>
+      <c r="N22" s="27"/>
+      <c r="O22" s="27"/>
+      <c r="P22" s="27"/>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E23" s="6" t="s">
         <v>297</v>
       </c>
-      <c r="F23" s="35" t="s">
+      <c r="F23" s="31" t="s">
         <v>298</v>
       </c>
-      <c r="G23" s="24"/>
-      <c r="H23" s="24"/>
-      <c r="I23" s="24"/>
-      <c r="J23" s="24"/>
-      <c r="K23" s="24"/>
-      <c r="L23" s="24"/>
-      <c r="M23" s="24"/>
-      <c r="N23" s="24"/>
-      <c r="O23" s="24"/>
-      <c r="P23" s="24"/>
+      <c r="G23" s="27"/>
+      <c r="H23" s="27"/>
+      <c r="I23" s="27"/>
+      <c r="J23" s="27"/>
+      <c r="K23" s="27"/>
+      <c r="L23" s="27"/>
+      <c r="M23" s="27"/>
+      <c r="N23" s="27"/>
+      <c r="O23" s="27"/>
+      <c r="P23" s="27"/>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A25" s="29" t="s">
+      <c r="A25" s="32" t="s">
         <v>299</v>
       </c>
-      <c r="B25" s="24"/>
-      <c r="C25" s="24"/>
-      <c r="D25" s="24"/>
+      <c r="B25" s="27"/>
+      <c r="C25" s="27"/>
+      <c r="D25" s="27"/>
       <c r="E25" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="F25" s="28" t="s">
+      <c r="F25" s="36" t="s">
         <v>300</v>
       </c>
-      <c r="G25" s="24"/>
-      <c r="H25" s="24"/>
-      <c r="I25" s="24"/>
-      <c r="J25" s="24"/>
-      <c r="K25" s="24"/>
-      <c r="L25" s="24"/>
-      <c r="M25" s="24"/>
-      <c r="N25" s="24"/>
-      <c r="O25" s="24"/>
-      <c r="P25" s="24"/>
+      <c r="G25" s="27"/>
+      <c r="H25" s="27"/>
+      <c r="I25" s="27"/>
+      <c r="J25" s="27"/>
+      <c r="K25" s="27"/>
+      <c r="L25" s="27"/>
+      <c r="M25" s="27"/>
+      <c r="N25" s="27"/>
+      <c r="O25" s="27"/>
+      <c r="P25" s="27"/>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E26" s="6" t="s">
@@ -4346,58 +4351,58 @@
       <c r="F26" s="33" t="s">
         <v>301</v>
       </c>
-      <c r="G26" s="24"/>
-      <c r="H26" s="24"/>
-      <c r="I26" s="24"/>
-      <c r="J26" s="24"/>
-      <c r="K26" s="24"/>
-      <c r="L26" s="24"/>
-      <c r="M26" s="24"/>
-      <c r="N26" s="24"/>
-      <c r="O26" s="24"/>
-      <c r="P26" s="24"/>
+      <c r="G26" s="27"/>
+      <c r="H26" s="27"/>
+      <c r="I26" s="27"/>
+      <c r="J26" s="27"/>
+      <c r="K26" s="27"/>
+      <c r="L26" s="27"/>
+      <c r="M26" s="27"/>
+      <c r="N26" s="27"/>
+      <c r="O26" s="27"/>
+      <c r="P26" s="27"/>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E27" s="6" t="s">
         <v>297</v>
       </c>
-      <c r="F27" s="35" t="s">
+      <c r="F27" s="31" t="s">
         <v>302</v>
       </c>
-      <c r="G27" s="24"/>
-      <c r="H27" s="24"/>
-      <c r="I27" s="24"/>
-      <c r="J27" s="24"/>
-      <c r="K27" s="24"/>
-      <c r="L27" s="24"/>
-      <c r="M27" s="24"/>
-      <c r="N27" s="24"/>
-      <c r="O27" s="24"/>
-      <c r="P27" s="24"/>
+      <c r="G27" s="27"/>
+      <c r="H27" s="27"/>
+      <c r="I27" s="27"/>
+      <c r="J27" s="27"/>
+      <c r="K27" s="27"/>
+      <c r="L27" s="27"/>
+      <c r="M27" s="27"/>
+      <c r="N27" s="27"/>
+      <c r="O27" s="27"/>
+      <c r="P27" s="27"/>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A29" s="29" t="s">
+      <c r="A29" s="32" t="s">
         <v>303</v>
       </c>
-      <c r="B29" s="24"/>
-      <c r="C29" s="24"/>
-      <c r="D29" s="24"/>
+      <c r="B29" s="27"/>
+      <c r="C29" s="27"/>
+      <c r="D29" s="27"/>
       <c r="E29" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="F29" s="28" t="s">
+      <c r="F29" s="36" t="s">
         <v>304</v>
       </c>
-      <c r="G29" s="24"/>
-      <c r="H29" s="24"/>
-      <c r="I29" s="24"/>
-      <c r="J29" s="24"/>
-      <c r="K29" s="24"/>
-      <c r="L29" s="24"/>
-      <c r="M29" s="24"/>
-      <c r="N29" s="24"/>
-      <c r="O29" s="24"/>
-      <c r="P29" s="24"/>
+      <c r="G29" s="27"/>
+      <c r="H29" s="27"/>
+      <c r="I29" s="27"/>
+      <c r="J29" s="27"/>
+      <c r="K29" s="27"/>
+      <c r="L29" s="27"/>
+      <c r="M29" s="27"/>
+      <c r="N29" s="27"/>
+      <c r="O29" s="27"/>
+      <c r="P29" s="27"/>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E30" s="6" t="s">
@@ -4406,145 +4411,137 @@
       <c r="F30" s="33" t="s">
         <v>305</v>
       </c>
-      <c r="G30" s="24"/>
-      <c r="H30" s="24"/>
-      <c r="I30" s="24"/>
-      <c r="J30" s="24"/>
-      <c r="K30" s="24"/>
-      <c r="L30" s="24"/>
-      <c r="M30" s="24"/>
-      <c r="N30" s="24"/>
-      <c r="O30" s="24"/>
-      <c r="P30" s="24"/>
+      <c r="G30" s="27"/>
+      <c r="H30" s="27"/>
+      <c r="I30" s="27"/>
+      <c r="J30" s="27"/>
+      <c r="K30" s="27"/>
+      <c r="L30" s="27"/>
+      <c r="M30" s="27"/>
+      <c r="N30" s="27"/>
+      <c r="O30" s="27"/>
+      <c r="P30" s="27"/>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E31" s="6" t="s">
         <v>297</v>
       </c>
-      <c r="F31" s="35" t="s">
+      <c r="F31" s="31" t="s">
         <v>306</v>
       </c>
-      <c r="G31" s="24"/>
-      <c r="H31" s="24"/>
-      <c r="I31" s="24"/>
-      <c r="J31" s="24"/>
-      <c r="K31" s="24"/>
-      <c r="L31" s="24"/>
-      <c r="M31" s="24"/>
-      <c r="N31" s="24"/>
-      <c r="O31" s="24"/>
-      <c r="P31" s="24"/>
+      <c r="G31" s="27"/>
+      <c r="H31" s="27"/>
+      <c r="I31" s="27"/>
+      <c r="J31" s="27"/>
+      <c r="K31" s="27"/>
+      <c r="L31" s="27"/>
+      <c r="M31" s="27"/>
+      <c r="N31" s="27"/>
+      <c r="O31" s="27"/>
+      <c r="P31" s="27"/>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A34" s="34" t="s">
+      <c r="A34" s="37" t="s">
         <v>307</v>
       </c>
-      <c r="B34" s="24"/>
-      <c r="C34" s="24"/>
-      <c r="D34" s="24"/>
-      <c r="E34" s="24"/>
-      <c r="F34" s="24"/>
-      <c r="G34" s="24"/>
-      <c r="H34" s="24"/>
-      <c r="I34" s="24"/>
-      <c r="J34" s="24"/>
-      <c r="K34" s="24"/>
-      <c r="L34" s="24"/>
-      <c r="M34" s="24"/>
-      <c r="N34" s="24"/>
-      <c r="O34" s="24"/>
-      <c r="P34" s="24"/>
+      <c r="B34" s="27"/>
+      <c r="C34" s="27"/>
+      <c r="D34" s="27"/>
+      <c r="E34" s="27"/>
+      <c r="F34" s="27"/>
+      <c r="G34" s="27"/>
+      <c r="H34" s="27"/>
+      <c r="I34" s="27"/>
+      <c r="J34" s="27"/>
+      <c r="K34" s="27"/>
+      <c r="L34" s="27"/>
+      <c r="M34" s="27"/>
+      <c r="N34" s="27"/>
+      <c r="O34" s="27"/>
+      <c r="P34" s="27"/>
     </row>
     <row r="36" spans="1:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="32" t="s">
+      <c r="A36" s="35" t="s">
         <v>308</v>
       </c>
-      <c r="B36" s="24"/>
-      <c r="C36" s="24"/>
-      <c r="D36" s="24"/>
-      <c r="E36" s="24"/>
-      <c r="F36" s="24"/>
-      <c r="G36" s="24"/>
-      <c r="H36" s="24"/>
-      <c r="I36" s="24"/>
-      <c r="J36" s="24"/>
-      <c r="K36" s="24"/>
-      <c r="L36" s="24"/>
-      <c r="M36" s="24"/>
-      <c r="N36" s="24"/>
-      <c r="O36" s="24"/>
-      <c r="P36" s="24"/>
+      <c r="B36" s="27"/>
+      <c r="C36" s="27"/>
+      <c r="D36" s="27"/>
+      <c r="E36" s="27"/>
+      <c r="F36" s="27"/>
+      <c r="G36" s="27"/>
+      <c r="H36" s="27"/>
+      <c r="I36" s="27"/>
+      <c r="J36" s="27"/>
+      <c r="K36" s="27"/>
+      <c r="L36" s="27"/>
+      <c r="M36" s="27"/>
+      <c r="N36" s="27"/>
+      <c r="O36" s="27"/>
+      <c r="P36" s="27"/>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A37" s="31" t="s">
+      <c r="A37" s="34" t="s">
         <v>309</v>
       </c>
-      <c r="B37" s="24"/>
-      <c r="C37" s="24"/>
-      <c r="D37" s="24"/>
-      <c r="E37" s="24"/>
-      <c r="F37" s="24"/>
-      <c r="G37" s="24"/>
-      <c r="H37" s="24"/>
-      <c r="I37" s="24"/>
-      <c r="J37" s="24"/>
-      <c r="K37" s="24"/>
-      <c r="L37" s="24"/>
-      <c r="M37" s="24"/>
-      <c r="N37" s="24"/>
-      <c r="O37" s="24"/>
-      <c r="P37" s="24"/>
+      <c r="B37" s="27"/>
+      <c r="C37" s="27"/>
+      <c r="D37" s="27"/>
+      <c r="E37" s="27"/>
+      <c r="F37" s="27"/>
+      <c r="G37" s="27"/>
+      <c r="H37" s="27"/>
+      <c r="I37" s="27"/>
+      <c r="J37" s="27"/>
+      <c r="K37" s="27"/>
+      <c r="L37" s="27"/>
+      <c r="M37" s="27"/>
+      <c r="N37" s="27"/>
+      <c r="O37" s="27"/>
+      <c r="P37" s="27"/>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A38" s="31" t="s">
+      <c r="A38" s="34" t="s">
         <v>310</v>
       </c>
-      <c r="B38" s="24"/>
-      <c r="C38" s="24"/>
-      <c r="D38" s="24"/>
-      <c r="E38" s="24"/>
-      <c r="F38" s="24"/>
-      <c r="G38" s="24"/>
-      <c r="H38" s="24"/>
-      <c r="I38" s="24"/>
-      <c r="J38" s="24"/>
-      <c r="K38" s="24"/>
-      <c r="L38" s="24"/>
-      <c r="M38" s="24"/>
-      <c r="N38" s="24"/>
-      <c r="O38" s="24"/>
-      <c r="P38" s="24"/>
+      <c r="B38" s="27"/>
+      <c r="C38" s="27"/>
+      <c r="D38" s="27"/>
+      <c r="E38" s="27"/>
+      <c r="F38" s="27"/>
+      <c r="G38" s="27"/>
+      <c r="H38" s="27"/>
+      <c r="I38" s="27"/>
+      <c r="J38" s="27"/>
+      <c r="K38" s="27"/>
+      <c r="L38" s="27"/>
+      <c r="M38" s="27"/>
+      <c r="N38" s="27"/>
+      <c r="O38" s="27"/>
+      <c r="P38" s="27"/>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A39" s="31" t="s">
+      <c r="A39" s="34" t="s">
         <v>311</v>
       </c>
-      <c r="B39" s="24"/>
-      <c r="C39" s="24"/>
-      <c r="D39" s="24"/>
-      <c r="E39" s="24"/>
-      <c r="F39" s="24"/>
-      <c r="G39" s="24"/>
-      <c r="H39" s="24"/>
-      <c r="I39" s="24"/>
-      <c r="J39" s="24"/>
-      <c r="K39" s="24"/>
-      <c r="L39" s="24"/>
-      <c r="M39" s="24"/>
-      <c r="N39" s="24"/>
-      <c r="O39" s="24"/>
-      <c r="P39" s="24"/>
+      <c r="B39" s="27"/>
+      <c r="C39" s="27"/>
+      <c r="D39" s="27"/>
+      <c r="E39" s="27"/>
+      <c r="F39" s="27"/>
+      <c r="G39" s="27"/>
+      <c r="H39" s="27"/>
+      <c r="I39" s="27"/>
+      <c r="J39" s="27"/>
+      <c r="K39" s="27"/>
+      <c r="L39" s="27"/>
+      <c r="M39" s="27"/>
+      <c r="N39" s="27"/>
+      <c r="O39" s="27"/>
+      <c r="P39" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="F23:P23"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="F22:P22"/>
-    <mergeCell ref="F31:P31"/>
-    <mergeCell ref="F27:P27"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A2:P2"/>
     <mergeCell ref="A38:P38"/>
     <mergeCell ref="A19:P19"/>
     <mergeCell ref="F30:P30"/>
@@ -4554,11 +4551,19 @@
     <mergeCell ref="F26:P26"/>
     <mergeCell ref="A36:P36"/>
     <mergeCell ref="A37:P37"/>
-    <mergeCell ref="A5:P5"/>
     <mergeCell ref="F29:P29"/>
     <mergeCell ref="A29:D29"/>
     <mergeCell ref="F25:P25"/>
     <mergeCell ref="A20:P20"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="F23:P23"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="F22:P22"/>
+    <mergeCell ref="F31:P31"/>
+    <mergeCell ref="F27:P27"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A2:P2"/>
+    <mergeCell ref="A5:P5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4566,7 +4571,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:P38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -4575,8 +4580,8 @@
     <col min="4" max="4" width="22" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
     <col min="6" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="26" customWidth="1"/>
+    <col min="7" max="7" width="25" customWidth="1"/>
+    <col min="8" max="8" width="26.85546875" customWidth="1"/>
     <col min="9" max="9" width="30" customWidth="1"/>
     <col min="10" max="10" width="16" customWidth="1"/>
     <col min="11" max="11" width="20" customWidth="1"/>
@@ -4587,24 +4592,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="30" t="s">
         <v>312</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
-      <c r="M1" s="24"/>
-      <c r="N1" s="24"/>
-      <c r="O1" s="24"/>
-      <c r="P1" s="24"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
+      <c r="O1" s="27"/>
+      <c r="P1" s="27"/>
     </row>
     <row r="3" spans="1:16" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
@@ -4656,314 +4661,1016 @@
         <v>85</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="26" t="s">
-        <v>313</v>
-      </c>
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="24"/>
-      <c r="G4" s="24"/>
-      <c r="H4" s="24"/>
-      <c r="I4" s="24"/>
-      <c r="J4" s="24"/>
-      <c r="K4" s="24"/>
-      <c r="L4" s="24"/>
-      <c r="M4" s="24"/>
-      <c r="N4" s="24"/>
-      <c r="O4" s="24"/>
-      <c r="P4" s="24"/>
-    </row>
-    <row r="5" spans="1:16" ht="48" x14ac:dyDescent="0.25">
-      <c r="A5" s="10">
+    <row r="4" spans="1:16" s="42" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="41" t="s">
+        <v>421</v>
+      </c>
+      <c r="B4" s="27"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
+      <c r="H4" s="27"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="27"/>
+      <c r="K4" s="27"/>
+      <c r="L4" s="27"/>
+      <c r="M4" s="27"/>
+      <c r="N4" s="27"/>
+      <c r="O4" s="27"/>
+      <c r="P4" s="27"/>
+    </row>
+    <row r="5" spans="1:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="40" t="s">
+        <v>422</v>
+      </c>
+      <c r="B5" s="43"/>
+      <c r="C5" s="43"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="43"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="43"/>
+      <c r="J5" s="43"/>
+      <c r="K5" s="43"/>
+      <c r="L5" s="43"/>
+      <c r="M5" s="43"/>
+      <c r="N5" s="43"/>
+      <c r="O5" s="43"/>
+      <c r="P5" s="43"/>
+    </row>
+    <row r="6" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+      <c r="A6" s="10">
         <v>1</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B6" s="45" t="s">
+        <v>410</v>
+      </c>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10" t="s">
         <v>314</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="F6" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="G6" s="45" t="s">
+        <v>416</v>
+      </c>
+      <c r="H6" s="10" t="s">
         <v>315</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="I6" s="10" t="s">
+        <v>417</v>
+      </c>
+      <c r="J6" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="K6" s="10" t="s">
         <v>316</v>
       </c>
-      <c r="E5" s="10" t="s">
-        <v>193</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="H5" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="I5" s="10" t="s">
+      <c r="L6" s="10" t="s">
         <v>317</v>
       </c>
-      <c r="J5" s="10" t="s">
+      <c r="M6" s="10" t="s">
+        <v>321</v>
+      </c>
+      <c r="N6" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="O6" s="10"/>
+      <c r="P6" s="10"/>
+    </row>
+    <row r="7" spans="1:16" ht="24" x14ac:dyDescent="0.25">
+      <c r="A7" s="10">
+        <v>2</v>
+      </c>
+      <c r="B7" s="10" t="s">
         <v>318</v>
       </c>
-      <c r="K5" s="10" t="s">
+      <c r="C7" s="10" t="s">
         <v>319</v>
       </c>
-      <c r="L5" s="10" t="s">
+      <c r="D7" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="M5" s="10" t="s">
+      <c r="E7" s="10" t="s">
+        <v>314</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="G7" s="45"/>
+      <c r="H7" s="10" t="s">
+        <v>315</v>
+      </c>
+      <c r="I7" s="39" t="s">
+        <v>418</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="M7" s="10" t="s">
         <v>321</v>
       </c>
-      <c r="N5" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="O5" s="10"/>
-      <c r="P5" s="10" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="36" t="s">
-        <v>323</v>
-      </c>
-      <c r="B7" s="24"/>
-      <c r="C7" s="24"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="24"/>
-      <c r="H7" s="24"/>
-      <c r="I7" s="24"/>
-      <c r="J7" s="24"/>
-      <c r="K7" s="24"/>
-      <c r="L7" s="24"/>
-      <c r="M7" s="24"/>
-      <c r="N7" s="24"/>
-      <c r="O7" s="24"/>
-      <c r="P7" s="24"/>
+      <c r="N7" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="O7" s="10"/>
+      <c r="P7" s="10"/>
     </row>
     <row r="8" spans="1:16" ht="24" x14ac:dyDescent="0.25">
       <c r="A8" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>324</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>325</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>326</v>
-      </c>
+        <v>411</v>
+      </c>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
       <c r="E8" s="10" t="s">
-        <v>327</v>
+        <v>314</v>
       </c>
       <c r="F8" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="G8" s="10" t="s">
-        <v>328</v>
-      </c>
+      <c r="G8" s="45"/>
       <c r="H8" s="10" t="s">
-        <v>329</v>
+        <v>315</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>330</v>
+        <v>419</v>
       </c>
       <c r="J8" s="10" t="s">
         <v>155</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>331</v>
+        <v>316</v>
       </c>
       <c r="L8" s="10" t="s">
-        <v>332</v>
+        <v>317</v>
       </c>
       <c r="M8" s="10" t="s">
-        <v>333</v>
-      </c>
-      <c r="N8" s="17" t="s">
-        <v>90</v>
+        <v>321</v>
+      </c>
+      <c r="N8" s="18" t="s">
+        <v>88</v>
       </c>
       <c r="O8" s="10"/>
-      <c r="P8" s="10" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" ht="24" x14ac:dyDescent="0.25">
-      <c r="A9" s="10">
-        <v>3</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>335</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>336</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>337</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>327</v>
-      </c>
-      <c r="F9" s="10" t="s">
+      <c r="P8" s="10"/>
+    </row>
+    <row r="10" spans="1:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="40" t="s">
+        <v>423</v>
+      </c>
+      <c r="B10" s="43"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="43"/>
+      <c r="J10" s="43"/>
+      <c r="K10" s="43"/>
+      <c r="L10" s="43"/>
+      <c r="M10" s="43"/>
+      <c r="N10" s="43"/>
+      <c r="O10" s="43"/>
+      <c r="P10" s="43"/>
+    </row>
+    <row r="11" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+      <c r="A11" s="10">
+        <v>1</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10" t="s">
+        <v>314</v>
+      </c>
+      <c r="F11" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="G9" s="10" t="s">
-        <v>328</v>
-      </c>
-      <c r="H9" s="10" t="s">
-        <v>329</v>
-      </c>
-      <c r="I9" s="10" t="s">
-        <v>338</v>
-      </c>
-      <c r="J9" s="10" t="s">
+      <c r="G11" s="45" t="s">
+        <v>426</v>
+      </c>
+      <c r="H11" s="10" t="s">
+        <v>315</v>
+      </c>
+      <c r="I11" s="39" t="s">
+        <v>417</v>
+      </c>
+      <c r="J11" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="K9" s="10" t="s">
-        <v>331</v>
-      </c>
-      <c r="L9" s="10" t="s">
-        <v>339</v>
-      </c>
-      <c r="M9" s="10" t="s">
-        <v>333</v>
-      </c>
-      <c r="N9" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="O9" s="10"/>
-      <c r="P9" s="10" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="36" t="s">
-        <v>341</v>
-      </c>
-      <c r="B11" s="24"/>
-      <c r="C11" s="24"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="24"/>
-      <c r="F11" s="24"/>
-      <c r="G11" s="24"/>
-      <c r="H11" s="24"/>
-      <c r="I11" s="24"/>
-      <c r="J11" s="24"/>
-      <c r="K11" s="24"/>
-      <c r="L11" s="24"/>
-      <c r="M11" s="24"/>
-      <c r="N11" s="24"/>
-      <c r="O11" s="24"/>
-      <c r="P11" s="24"/>
-    </row>
-    <row r="12" spans="1:16" ht="24" x14ac:dyDescent="0.25">
+      <c r="K11" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="L11" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="M11" s="10" t="s">
+        <v>321</v>
+      </c>
+      <c r="N11" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="O11" s="10"/>
+      <c r="P11" s="10"/>
+    </row>
+    <row r="12" spans="1:16" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>342</v>
+        <v>318</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>343</v>
+        <v>319</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>344</v>
+        <v>320</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>327</v>
+        <v>314</v>
       </c>
       <c r="F12" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="G12" s="10" t="s">
-        <v>345</v>
+      <c r="G12" s="45" t="s">
+        <v>426</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>329</v>
-      </c>
-      <c r="I12" s="10" t="s">
-        <v>346</v>
+        <v>315</v>
+      </c>
+      <c r="I12" s="39" t="s">
+        <v>418</v>
       </c>
       <c r="J12" s="10" t="s">
         <v>155</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>331</v>
+        <v>316</v>
       </c>
       <c r="L12" s="10" t="s">
-        <v>332</v>
+        <v>317</v>
       </c>
       <c r="M12" s="10" t="s">
-        <v>347</v>
-      </c>
-      <c r="N12" s="17" t="s">
-        <v>90</v>
+        <v>321</v>
+      </c>
+      <c r="N12" s="18" t="s">
+        <v>88</v>
       </c>
       <c r="O12" s="10"/>
-      <c r="P12" s="10" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" ht="24" x14ac:dyDescent="0.25">
+      <c r="P12" s="10"/>
+    </row>
+    <row r="13" spans="1:16" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>349</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>350</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>351</v>
-      </c>
+        <v>411</v>
+      </c>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
       <c r="E13" s="10" t="s">
-        <v>327</v>
+        <v>314</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>352</v>
+        <v>207</v>
+      </c>
+      <c r="G13" s="45" t="s">
+        <v>426</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>329</v>
-      </c>
-      <c r="I13" s="10" t="s">
-        <v>353</v>
+        <v>315</v>
+      </c>
+      <c r="I13" s="39" t="s">
+        <v>419</v>
       </c>
       <c r="J13" s="10" t="s">
         <v>155</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>331</v>
+        <v>316</v>
       </c>
       <c r="L13" s="10" t="s">
-        <v>354</v>
+        <v>317</v>
       </c>
       <c r="M13" s="10" t="s">
-        <v>347</v>
-      </c>
-      <c r="N13" s="17" t="s">
-        <v>90</v>
+        <v>321</v>
+      </c>
+      <c r="N13" s="18" t="s">
+        <v>88</v>
       </c>
       <c r="O13" s="10"/>
-      <c r="P13" s="10" t="s">
-        <v>355</v>
-      </c>
-    </row>
+      <c r="P13" s="10"/>
+    </row>
+    <row r="14" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+      <c r="A14" s="10">
+        <v>4</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>412</v>
+      </c>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10" t="s">
+        <v>314</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="G14" s="45" t="s">
+        <v>426</v>
+      </c>
+      <c r="H14" s="10" t="s">
+        <v>315</v>
+      </c>
+      <c r="I14" s="39" t="s">
+        <v>420</v>
+      </c>
+      <c r="J14" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="K14" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="L14" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="M14" s="10" t="s">
+        <v>321</v>
+      </c>
+      <c r="N14" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="O14" s="10"/>
+      <c r="P14" s="10"/>
+    </row>
+    <row r="16" spans="1:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="40" t="s">
+        <v>427</v>
+      </c>
+      <c r="B16" s="43"/>
+      <c r="C16" s="43"/>
+      <c r="D16" s="43"/>
+      <c r="E16" s="43"/>
+      <c r="F16" s="43"/>
+      <c r="G16" s="43"/>
+      <c r="H16" s="43"/>
+      <c r="I16" s="43"/>
+      <c r="J16" s="43"/>
+      <c r="K16" s="43"/>
+      <c r="L16" s="43"/>
+      <c r="M16" s="43"/>
+      <c r="N16" s="43"/>
+      <c r="O16" s="43"/>
+      <c r="P16" s="43"/>
+    </row>
+    <row r="17" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+      <c r="A17" s="10">
+        <v>1</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10" t="s">
+        <v>314</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="G17" s="45" t="s">
+        <v>428</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>315</v>
+      </c>
+      <c r="I17" s="39" t="s">
+        <v>417</v>
+      </c>
+      <c r="J17" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="K17" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="L17" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="M17" s="10" t="s">
+        <v>321</v>
+      </c>
+      <c r="N17" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="O17" s="10"/>
+      <c r="P17" s="10"/>
+    </row>
+    <row r="18" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+      <c r="A18" s="10">
+        <v>2</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>319</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>320</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>314</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="G18" s="45" t="s">
+        <v>428</v>
+      </c>
+      <c r="H18" s="10" t="s">
+        <v>315</v>
+      </c>
+      <c r="I18" s="39" t="s">
+        <v>418</v>
+      </c>
+      <c r="J18" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="K18" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="L18" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="M18" s="10" t="s">
+        <v>321</v>
+      </c>
+      <c r="N18" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="O18" s="10"/>
+      <c r="P18" s="10"/>
+    </row>
+    <row r="20" spans="1:16" s="44" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="41" t="s">
+        <v>424</v>
+      </c>
+      <c r="B20" s="27"/>
+      <c r="C20" s="27"/>
+      <c r="D20" s="27"/>
+      <c r="E20" s="27"/>
+      <c r="F20" s="27"/>
+      <c r="G20" s="27"/>
+      <c r="H20" s="27"/>
+      <c r="I20" s="27"/>
+      <c r="J20" s="27"/>
+      <c r="K20" s="27"/>
+      <c r="L20" s="27"/>
+      <c r="M20" s="27"/>
+      <c r="N20" s="27"/>
+      <c r="O20" s="27"/>
+      <c r="P20" s="27"/>
+    </row>
+    <row r="21" spans="1:16" s="44" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="40" t="s">
+        <v>425</v>
+      </c>
+      <c r="B21" s="43"/>
+      <c r="C21" s="43"/>
+      <c r="D21" s="43"/>
+      <c r="E21" s="43"/>
+      <c r="F21" s="43"/>
+      <c r="G21" s="43"/>
+      <c r="H21" s="43"/>
+      <c r="I21" s="43"/>
+      <c r="J21" s="43"/>
+      <c r="K21" s="43"/>
+      <c r="L21" s="43"/>
+      <c r="M21" s="43"/>
+      <c r="N21" s="43"/>
+      <c r="O21" s="43"/>
+      <c r="P21" s="43"/>
+    </row>
+    <row r="22" spans="1:16" s="44" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A22" s="10">
+        <v>1</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>319</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>320</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>314</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="G22" s="45" t="s">
+        <v>426</v>
+      </c>
+      <c r="H22" s="10" t="s">
+        <v>315</v>
+      </c>
+      <c r="I22" s="45" t="s">
+        <v>418</v>
+      </c>
+      <c r="J22" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="K22" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="L22" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="M22" s="10" t="s">
+        <v>321</v>
+      </c>
+      <c r="N22" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="O22" s="10"/>
+      <c r="P22" s="10"/>
+    </row>
+    <row r="23" spans="1:16" s="44" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A23" s="10">
+        <v>2</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>411</v>
+      </c>
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10" t="s">
+        <v>314</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="G23" s="45" t="s">
+        <v>426</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>315</v>
+      </c>
+      <c r="I23" s="45" t="s">
+        <v>419</v>
+      </c>
+      <c r="J23" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="K23" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="L23" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="M23" s="10" t="s">
+        <v>321</v>
+      </c>
+      <c r="N23" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="O23" s="10"/>
+      <c r="P23" s="10"/>
+    </row>
+    <row r="24" spans="1:16" s="44" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A24" s="10">
+        <v>3</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>412</v>
+      </c>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10" t="s">
+        <v>314</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="G24" s="45" t="s">
+        <v>426</v>
+      </c>
+      <c r="H24" s="10" t="s">
+        <v>315</v>
+      </c>
+      <c r="I24" s="45" t="s">
+        <v>420</v>
+      </c>
+      <c r="J24" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="K24" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="L24" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="M24" s="10" t="s">
+        <v>321</v>
+      </c>
+      <c r="N24" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="O24" s="10"/>
+      <c r="P24" s="10"/>
+    </row>
+    <row r="26" spans="1:16" s="44" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="40" t="s">
+        <v>429</v>
+      </c>
+      <c r="B26" s="43"/>
+      <c r="C26" s="43"/>
+      <c r="D26" s="43"/>
+      <c r="E26" s="43"/>
+      <c r="F26" s="43"/>
+      <c r="G26" s="43"/>
+      <c r="H26" s="43"/>
+      <c r="I26" s="43"/>
+      <c r="J26" s="43"/>
+      <c r="K26" s="43"/>
+      <c r="L26" s="43"/>
+      <c r="M26" s="43"/>
+      <c r="N26" s="43"/>
+      <c r="O26" s="43"/>
+      <c r="P26" s="43"/>
+    </row>
+    <row r="27" spans="1:16" s="44" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A27" s="10">
+        <v>1</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>413</v>
+      </c>
+      <c r="C27" s="10"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="10" t="s">
+        <v>314</v>
+      </c>
+      <c r="F27" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="G27" s="45" t="s">
+        <v>431</v>
+      </c>
+      <c r="H27" s="10" t="s">
+        <v>315</v>
+      </c>
+      <c r="I27" s="45" t="s">
+        <v>432</v>
+      </c>
+      <c r="J27" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="K27" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="L27" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="M27" s="10" t="s">
+        <v>321</v>
+      </c>
+      <c r="N27" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="O27" s="10"/>
+      <c r="P27" s="10"/>
+    </row>
+    <row r="28" spans="1:16" s="44" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A28" s="10">
+        <v>2</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>414</v>
+      </c>
+      <c r="C28" s="10"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10" t="s">
+        <v>314</v>
+      </c>
+      <c r="F28" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="G28" s="45" t="s">
+        <v>431</v>
+      </c>
+      <c r="H28" s="10" t="s">
+        <v>315</v>
+      </c>
+      <c r="I28" s="45" t="s">
+        <v>433</v>
+      </c>
+      <c r="J28" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="K28" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="L28" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="M28" s="10" t="s">
+        <v>321</v>
+      </c>
+      <c r="N28" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="O28" s="10"/>
+      <c r="P28" s="10"/>
+    </row>
+    <row r="29" spans="1:16" s="44" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A29" s="10">
+        <v>3</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>415</v>
+      </c>
+      <c r="C29" s="10"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="10" t="s">
+        <v>314</v>
+      </c>
+      <c r="F29" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="G29" s="45" t="s">
+        <v>431</v>
+      </c>
+      <c r="H29" s="10" t="s">
+        <v>315</v>
+      </c>
+      <c r="I29" s="45" t="s">
+        <v>434</v>
+      </c>
+      <c r="J29" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="K29" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="L29" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="M29" s="10" t="s">
+        <v>321</v>
+      </c>
+      <c r="N29" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="O29" s="10"/>
+      <c r="P29" s="10"/>
+    </row>
+    <row r="31" spans="1:16" s="44" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="40" t="s">
+        <v>430</v>
+      </c>
+      <c r="B31" s="43"/>
+      <c r="C31" s="43"/>
+      <c r="D31" s="43"/>
+      <c r="E31" s="43"/>
+      <c r="F31" s="43"/>
+      <c r="G31" s="43"/>
+      <c r="H31" s="43"/>
+      <c r="I31" s="43"/>
+      <c r="J31" s="43"/>
+      <c r="K31" s="43"/>
+      <c r="L31" s="43"/>
+      <c r="M31" s="43"/>
+      <c r="N31" s="43"/>
+      <c r="O31" s="43"/>
+      <c r="P31" s="43"/>
+    </row>
+    <row r="32" spans="1:16" s="44" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A32" s="10">
+        <v>1</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>413</v>
+      </c>
+      <c r="C32" s="10"/>
+      <c r="D32" s="10"/>
+      <c r="E32" s="10" t="s">
+        <v>314</v>
+      </c>
+      <c r="F32" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="G32" s="45" t="s">
+        <v>431</v>
+      </c>
+      <c r="H32" s="10" t="s">
+        <v>315</v>
+      </c>
+      <c r="I32" s="45" t="s">
+        <v>432</v>
+      </c>
+      <c r="J32" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="K32" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="L32" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="M32" s="10" t="s">
+        <v>321</v>
+      </c>
+      <c r="N32" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="O32" s="10"/>
+      <c r="P32" s="10"/>
+    </row>
+    <row r="33" spans="1:16" s="44" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A33" s="10">
+        <v>2</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>414</v>
+      </c>
+      <c r="C33" s="10"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="10" t="s">
+        <v>314</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="G33" s="45" t="s">
+        <v>431</v>
+      </c>
+      <c r="H33" s="10" t="s">
+        <v>315</v>
+      </c>
+      <c r="I33" s="45" t="s">
+        <v>433</v>
+      </c>
+      <c r="J33" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="K33" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="L33" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="M33" s="10" t="s">
+        <v>321</v>
+      </c>
+      <c r="N33" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="O33" s="10"/>
+      <c r="P33" s="10"/>
+    </row>
+    <row r="34" spans="1:16" s="44" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A34" s="10">
+        <v>3</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>415</v>
+      </c>
+      <c r="C34" s="10"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="10" t="s">
+        <v>314</v>
+      </c>
+      <c r="F34" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="G34" s="45" t="s">
+        <v>431</v>
+      </c>
+      <c r="H34" s="10" t="s">
+        <v>315</v>
+      </c>
+      <c r="I34" s="45" t="s">
+        <v>434</v>
+      </c>
+      <c r="J34" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="K34" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="L34" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="M34" s="10" t="s">
+        <v>321</v>
+      </c>
+      <c r="N34" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="O34" s="10"/>
+      <c r="P34" s="10"/>
+    </row>
+    <row r="36" spans="1:16" s="44" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="40" t="s">
+        <v>435</v>
+      </c>
+      <c r="B36" s="43"/>
+      <c r="C36" s="43"/>
+      <c r="D36" s="43"/>
+      <c r="E36" s="43"/>
+      <c r="F36" s="43"/>
+      <c r="G36" s="43"/>
+      <c r="H36" s="43"/>
+      <c r="I36" s="43"/>
+      <c r="J36" s="43"/>
+      <c r="K36" s="43"/>
+      <c r="L36" s="43"/>
+      <c r="M36" s="43"/>
+      <c r="N36" s="43"/>
+      <c r="O36" s="43"/>
+      <c r="P36" s="43"/>
+    </row>
+    <row r="37" spans="1:16" s="44" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A37" s="10">
+        <v>1</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>319</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>320</v>
+      </c>
+      <c r="E37" s="10" t="s">
+        <v>314</v>
+      </c>
+      <c r="F37" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="G37" s="45" t="s">
+        <v>428</v>
+      </c>
+      <c r="H37" s="10" t="s">
+        <v>315</v>
+      </c>
+      <c r="I37" s="45" t="s">
+        <v>418</v>
+      </c>
+      <c r="J37" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="K37" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="L37" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="M37" s="10" t="s">
+        <v>321</v>
+      </c>
+      <c r="N37" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="O37" s="10"/>
+      <c r="P37" s="10"/>
+    </row>
+    <row r="38" spans="1:16" s="44" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A11:P11"/>
+  <mergeCells count="10">
+    <mergeCell ref="A36:P36"/>
+    <mergeCell ref="A20:P20"/>
+    <mergeCell ref="A4:P4"/>
+    <mergeCell ref="A21:P21"/>
+    <mergeCell ref="A26:P26"/>
+    <mergeCell ref="A31:P31"/>
+    <mergeCell ref="A10:P10"/>
+    <mergeCell ref="A16:P16"/>
     <mergeCell ref="A1:P1"/>
-    <mergeCell ref="A7:P7"/>
-    <mergeCell ref="A4:P4"/>
+    <mergeCell ref="A5:P5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4980,21 +5687,21 @@
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
-        <v>356</v>
+        <v>322</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="20" t="s">
-        <v>357</v>
+        <v>323</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>358</v>
+        <v>324</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>359</v>
+        <v>325</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>360</v>
+        <v>326</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="24" x14ac:dyDescent="0.25">
@@ -5002,13 +5709,13 @@
         <v>120</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>361</v>
+        <v>327</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>362</v>
+        <v>328</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>363</v>
+        <v>329</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -5016,13 +5723,13 @@
         <v>103</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>361</v>
+        <v>327</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>364</v>
+        <v>330</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>365</v>
+        <v>331</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="24" x14ac:dyDescent="0.25">
@@ -5030,13 +5737,13 @@
         <v>139</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>366</v>
+        <v>332</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>367</v>
+        <v>333</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>368</v>
+        <v>334</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="60" x14ac:dyDescent="0.25">
@@ -5044,41 +5751,41 @@
         <v>232</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>369</v>
+        <v>335</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>370</v>
+        <v>336</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>371</v>
+        <v>337</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="36" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>372</v>
+        <v>338</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>373</v>
+        <v>339</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>374</v>
+        <v>340</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>375</v>
+        <v>341</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="36" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>329</v>
+        <v>315</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>361</v>
+        <v>327</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>376</v>
+        <v>342</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>377</v>
+        <v>343</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -5086,27 +5793,27 @@
         <v>156</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>361</v>
+        <v>327</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>378</v>
+        <v>344</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>379</v>
+        <v>345</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="24" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>380</v>
+        <v>346</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>361</v>
+        <v>327</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>381</v>
+        <v>347</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>382</v>
+        <v>348</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="24" x14ac:dyDescent="0.25">
@@ -5114,13 +5821,13 @@
         <v>215</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>361</v>
+        <v>327</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>383</v>
+        <v>349</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>384</v>
+        <v>350</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="24" x14ac:dyDescent="0.25">
@@ -5128,41 +5835,41 @@
         <v>248</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>361</v>
+        <v>327</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>385</v>
+        <v>351</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>386</v>
+        <v>352</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="36" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>387</v>
+        <v>353</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>361</v>
+        <v>327</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>388</v>
+        <v>354</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>389</v>
+        <v>355</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="24" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>331</v>
+        <v>316</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>390</v>
+        <v>356</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>391</v>
+        <v>357</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>392</v>
+        <v>358</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -5170,13 +5877,13 @@
         <v>105</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>361</v>
+        <v>327</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>393</v>
+        <v>359</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>386</v>
+        <v>352</v>
       </c>
     </row>
   </sheetData>
@@ -5198,29 +5905,29 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>394</v>
+        <v>360</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>395</v>
+        <v>361</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="20" t="s">
-        <v>396</v>
+        <v>362</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>397</v>
+        <v>363</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>398</v>
+        <v>364</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>399</v>
+        <v>365</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>400</v>
+        <v>366</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -5228,46 +5935,46 @@
         <v>1</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>401</v>
+        <v>367</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>402</v>
+        <v>368</v>
       </c>
       <c r="D5" s="22" t="s">
         <v>284</v>
       </c>
-      <c r="E5" s="37"/>
+      <c r="E5" s="23"/>
     </row>
     <row r="6" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="21">
         <v>2</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>401</v>
+        <v>367</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>403</v>
+        <v>369</v>
       </c>
       <c r="D6" s="22" t="s">
         <v>268</v>
       </c>
-      <c r="E6" s="37"/>
+      <c r="E6" s="23"/>
     </row>
     <row r="7" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="21">
         <v>3</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>401</v>
+        <v>367</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>404</v>
+        <v>370</v>
       </c>
       <c r="D7" s="22" t="s">
         <v>231</v>
       </c>
-      <c r="E7" s="37" t="s">
-        <v>439</v>
+      <c r="E7" s="23" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -5275,61 +5982,61 @@
         <v>4</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>401</v>
+        <v>367</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>405</v>
+        <v>371</v>
       </c>
       <c r="D8" s="22" t="s">
         <v>253</v>
       </c>
-      <c r="E8" s="37"/>
+      <c r="E8" s="23"/>
     </row>
     <row r="9" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="21">
         <v>5</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>406</v>
+        <v>372</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>407</v>
+        <v>373</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>316</v>
-      </c>
-      <c r="E9" s="37"/>
+        <v>313</v>
+      </c>
+      <c r="E9" s="23"/>
     </row>
     <row r="10" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="21">
         <v>6</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>406</v>
+        <v>372</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>408</v>
+        <v>374</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>409</v>
-      </c>
-      <c r="E10" s="37"/>
+        <v>375</v>
+      </c>
+      <c r="E10" s="23"/>
     </row>
     <row r="11" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="21">
         <v>7</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>411</v>
+        <v>377</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>412</v>
-      </c>
-      <c r="E11" s="37" t="s">
-        <v>440</v>
+        <v>378</v>
+      </c>
+      <c r="E11" s="23" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -5337,16 +6044,16 @@
         <v>8</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>413</v>
+        <v>379</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>414</v>
+        <v>380</v>
       </c>
       <c r="D12" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="E12" s="37" t="s">
-        <v>441</v>
+      <c r="E12" s="23" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -5354,16 +6061,16 @@
         <v>9</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>415</v>
-      </c>
-      <c r="C13" s="38" t="s">
-        <v>416</v>
+        <v>381</v>
+      </c>
+      <c r="C13" s="24" t="s">
+        <v>382</v>
       </c>
       <c r="D13" s="22" t="s">
-        <v>417</v>
-      </c>
-      <c r="E13" s="39" t="s">
-        <v>442</v>
+        <v>383</v>
+      </c>
+      <c r="E13" s="25" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -5371,61 +6078,61 @@
         <v>10</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>415</v>
+        <v>381</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>418</v>
+        <v>384</v>
       </c>
       <c r="D14" s="22" t="s">
-        <v>419</v>
-      </c>
-      <c r="E14" s="37"/>
+        <v>385</v>
+      </c>
+      <c r="E14" s="23"/>
     </row>
     <row r="15" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="21">
         <v>11</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>420</v>
+        <v>386</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>421</v>
+        <v>387</v>
       </c>
       <c r="D15" s="22" t="s">
-        <v>422</v>
-      </c>
-      <c r="E15" s="37"/>
+        <v>388</v>
+      </c>
+      <c r="E15" s="23"/>
     </row>
     <row r="16" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="21">
         <v>12</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>423</v>
+        <v>389</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>424</v>
+        <v>390</v>
       </c>
       <c r="D16" s="22" t="s">
-        <v>425</v>
-      </c>
-      <c r="E16" s="37"/>
+        <v>391</v>
+      </c>
+      <c r="E16" s="23"/>
     </row>
     <row r="17" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="21">
         <v>13</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>413</v>
+        <v>379</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>426</v>
+        <v>392</v>
       </c>
       <c r="D17" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="E17" s="37" t="s">
-        <v>443</v>
+      <c r="E17" s="23" t="s">
+        <v>409</v>
       </c>
     </row>
   </sheetData>
